--- a/MCDA_Ratings_Werkspoor.xlsx
+++ b/MCDA_Ratings_Werkspoor.xlsx
@@ -1,26 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tvanr\OneDrive\Documenten\BASE\Structural-group-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Structural-group-5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D4F73BB-81E9-4B4A-88D9-5484C0928C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB86BD7-3DA8-4669-A059-008E3730C985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
   </bookViews>
   <sheets>
-    <sheet name="MCDA_Ratings_Werkspoor" sheetId="1" r:id="rId1"/>
+    <sheet name="Nature by Prajwal" sheetId="4" r:id="rId1"/>
+    <sheet name="Companies by Thijs" sheetId="3" r:id="rId2"/>
+    <sheet name="Government by Thijmen" sheetId="2" r:id="rId3"/>
+    <sheet name="Citizen by Amit" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="35">
   <si>
     <t>MCDA Gold Coast Design Alternatives</t>
   </si>
@@ -131,7 +139,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -636,24 +644,24 @@
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Berekening" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Controlecel" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Gekoppelde cel" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Goed" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Invoer" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Kop 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Kop 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Kop 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Kop 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Neutraal" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Notitie" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Ongeldig" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
-    <cellStyle name="Titel" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Totaal" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Uitvoer" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Verklarende tekst" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Waarschuwingstekst" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -984,16 +992,1270 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E21EC2-64DE-445B-8154-60469756B239}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>80</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>25</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5">
+        <v>50</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>80</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>75</v>
+      </c>
+      <c r="F7">
+        <v>75</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>80</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>70</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>75</v>
+      </c>
+      <c r="F11">
+        <v>75</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12">
+        <v>80</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>50</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>100</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15">
+        <v>100</v>
+      </c>
+      <c r="D15">
+        <v>90</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>80</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>70</v>
+      </c>
+      <c r="D18">
+        <v>100</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A898AA9E-6EE8-44A9-9DEF-7D9FA314DBCA}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>80</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>25</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5">
+        <v>50</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>80</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>75</v>
+      </c>
+      <c r="F7">
+        <v>75</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>80</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>70</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>75</v>
+      </c>
+      <c r="F11">
+        <v>75</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12">
+        <v>80</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>50</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>100</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15">
+        <v>100</v>
+      </c>
+      <c r="D15">
+        <v>90</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>80</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>70</v>
+      </c>
+      <c r="D18">
+        <v>100</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E73D97-BC3F-49A1-B8F4-F095906B505B}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>80</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>25</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5">
+        <v>50</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>80</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>75</v>
+      </c>
+      <c r="F7">
+        <v>75</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>80</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>70</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>75</v>
+      </c>
+      <c r="F11">
+        <v>75</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12">
+        <v>80</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>50</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>100</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15">
+        <v>100</v>
+      </c>
+      <c r="D15">
+        <v>90</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>80</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>70</v>
+      </c>
+      <c r="D18">
+        <v>100</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A57D4CE-8BDF-4BD2-8CFC-2B5D7CFE333B}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1016,7 +2278,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1039,7 +2301,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1062,7 +2324,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1085,7 +2347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1108,7 +2370,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1131,7 +2393,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1154,7 +2416,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1177,7 +2439,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1200,7 +2462,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1223,7 +2485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1246,7 +2508,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1269,7 +2531,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1292,7 +2554,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1315,7 +2577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1338,7 +2600,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1361,7 +2623,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>34</v>
       </c>

--- a/MCDA_Ratings_Werkspoor.xlsx
+++ b/MCDA_Ratings_Werkspoor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Structural-group-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Amit/Documents/GitHub/Structural-group-5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB86BD7-3DA8-4669-A059-008E3730C985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D85B58D-B248-134F-ACDE-2F7918FE05F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
+    <workbookView xWindow="2320" yWindow="500" windowWidth="26480" windowHeight="16060" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Nature by Prajwal" sheetId="4" r:id="rId1"/>
@@ -18,17 +18,25 @@
     <sheet name="Government by Thijmen" sheetId="2" r:id="rId3"/>
     <sheet name="Citizen by Amit" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="71">
   <si>
     <t>MCDA Gold Coast Design Alternatives</t>
   </si>
@@ -133,13 +141,121 @@
   </si>
   <si>
     <t>Tourist Sector</t>
+  </si>
+  <si>
+    <t>Railway functionality</t>
+  </si>
+  <si>
+    <t>tunnel</t>
+  </si>
+  <si>
+    <t>don’t widen river</t>
+  </si>
+  <si>
+    <t>City Citizens</t>
+  </si>
+  <si>
+    <t>Construction Disruption</t>
+  </si>
+  <si>
+    <t>truss bridge</t>
+  </si>
+  <si>
+    <t>use another bridge</t>
+  </si>
+  <si>
+    <t>Visual appeal</t>
+  </si>
+  <si>
+    <t>reasoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demka would remain operational </t>
+  </si>
+  <si>
+    <t>new bridge while demka is renovated</t>
+  </si>
+  <si>
+    <t>track remains opperational</t>
+  </si>
+  <si>
+    <t>tunnel not as safe due to fires, floods, whatever will make pedestrians need to evacuate</t>
+  </si>
+  <si>
+    <t>Werkspoor bridge alternative solutions</t>
+  </si>
+  <si>
+    <t>eliminates construction related risks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>stable bridge, but introduces large exposed structure</t>
+  </si>
+  <si>
+    <t>transport lines still opperational but need to detour to another bridge. Not convinient. Also, less capacity</t>
+  </si>
+  <si>
+    <t>pedestrians can safely use another bridge</t>
+  </si>
+  <si>
+    <t>Long-term functionality</t>
+  </si>
+  <si>
+    <t>tunnel can remain opperational</t>
+  </si>
+  <si>
+    <t>river needs to be widened to meet increasing shipping demands</t>
+  </si>
+  <si>
+    <t>not as pretty as Werkspoor bridge</t>
+  </si>
+  <si>
+    <t>reliable and sustainable long term solution</t>
+  </si>
+  <si>
+    <t>will put too much pressure on surrounding transit lines that will likely exceed its capacity, as it was not deisgned to accommodate</t>
+  </si>
+  <si>
+    <t>lots of noise and distruption to ground due to drilling the tunnel hole</t>
+  </si>
+  <si>
+    <t>no contruction required</t>
+  </si>
+  <si>
+    <t>large scale construction project</t>
+  </si>
+  <si>
+    <t>this would require transit lines to increase their capacity to accommodate, lots of contruction will be required</t>
+  </si>
+  <si>
+    <t>tunnel construction can have significant enviornmental impacts</t>
+  </si>
+  <si>
+    <t>avoids new construction project</t>
+  </si>
+  <si>
+    <t>bridge construction project will have lots of enviornmenatal impacts</t>
+  </si>
+  <si>
+    <t>will reuse existing infrastructure but that infrastructure will need to be upgraded and will thus demand construction, causing environmental impacts</t>
+  </si>
+  <si>
+    <t>most of tunnel infrastructure is underrground so it does not imact the visuals of the area</t>
+  </si>
+  <si>
+    <t>no new construction project required</t>
+  </si>
+  <si>
+    <t>existing transit infrastructure will need to be renovated to accommodate increased demand, can potentially affect visual appeal of area</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -993,24 +1109,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E21EC2-64DE-445B-8154-60469756B239}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:P23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.9140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5" customWidth="1"/>
+    <col min="13" max="13" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="J1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1032,8 +1158,29 @@
       <c r="G2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="J2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1055,8 +1202,29 @@
       <c r="G3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="J3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3">
+        <v>100</v>
+      </c>
+      <c r="M3">
+        <v>80</v>
+      </c>
+      <c r="N3">
+        <v>100</v>
+      </c>
+      <c r="O3">
+        <v>40</v>
+      </c>
+      <c r="P3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1078,8 +1246,29 @@
       <c r="G4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4">
+        <v>60</v>
+      </c>
+      <c r="M4">
+        <v>80</v>
+      </c>
+      <c r="N4">
+        <v>90</v>
+      </c>
+      <c r="O4">
+        <v>70</v>
+      </c>
+      <c r="P4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1101,8 +1290,29 @@
       <c r="G5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="J5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5">
+        <v>40</v>
+      </c>
+      <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
+        <v>50</v>
+      </c>
+      <c r="O5">
+        <v>30</v>
+      </c>
+      <c r="P5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1124,8 +1334,29 @@
       <c r="G6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="J6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6">
+        <v>80</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+      <c r="N6">
+        <v>80</v>
+      </c>
+      <c r="O6">
+        <v>30</v>
+      </c>
+      <c r="P6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1147,8 +1378,29 @@
       <c r="G7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="J7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7">
+        <v>50</v>
+      </c>
+      <c r="M7">
+        <v>90</v>
+      </c>
+      <c r="N7">
+        <v>50</v>
+      </c>
+      <c r="O7">
+        <v>60</v>
+      </c>
+      <c r="P7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1170,8 +1422,29 @@
       <c r="G8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8">
+        <v>80</v>
+      </c>
+      <c r="M8">
+        <v>95</v>
+      </c>
+      <c r="N8">
+        <v>50</v>
+      </c>
+      <c r="O8">
+        <v>60</v>
+      </c>
+      <c r="P8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1194,7 +1467,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1217,7 +1490,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1240,7 +1513,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1263,7 +1536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1286,7 +1559,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1308,8 +1581,11 @@
       <c r="G14" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="M14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1332,7 +1608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1354,8 +1630,11 @@
       <c r="G16" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="J16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1377,8 +1656,29 @@
       <c r="G17" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="J17" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" t="s">
+        <v>2</v>
+      </c>
+      <c r="L17" t="s">
+        <v>36</v>
+      </c>
+      <c r="M17" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" t="s">
+        <v>40</v>
+      </c>
+      <c r="O17" t="s">
+        <v>41</v>
+      </c>
+      <c r="P17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1398,6 +1698,142 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" t="s">
+        <v>35</v>
+      </c>
+      <c r="L18" t="s">
+        <v>46</v>
+      </c>
+      <c r="M18" t="s">
+        <v>44</v>
+      </c>
+      <c r="N18" t="s">
+        <v>45</v>
+      </c>
+      <c r="O18" t="s">
+        <v>52</v>
+      </c>
+      <c r="P18">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K19" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M19" t="s">
+        <v>49</v>
+      </c>
+      <c r="N19" t="s">
+        <v>51</v>
+      </c>
+      <c r="O19" t="s">
+        <v>53</v>
+      </c>
+      <c r="P19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J20" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" t="s">
+        <v>39</v>
+      </c>
+      <c r="L20" t="s">
+        <v>60</v>
+      </c>
+      <c r="M20" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" t="s">
+        <v>62</v>
+      </c>
+      <c r="O20" t="s">
+        <v>63</v>
+      </c>
+      <c r="P20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J21" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" t="s">
+        <v>54</v>
+      </c>
+      <c r="L21" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" t="s">
+        <v>56</v>
+      </c>
+      <c r="N21" t="s">
+        <v>58</v>
+      </c>
+      <c r="O21" t="s">
+        <v>59</v>
+      </c>
+      <c r="P21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J22" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" t="s">
+        <v>64</v>
+      </c>
+      <c r="M22" t="s">
+        <v>65</v>
+      </c>
+      <c r="N22" t="s">
+        <v>66</v>
+      </c>
+      <c r="O22" t="s">
+        <v>67</v>
+      </c>
+      <c r="P22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J23" t="s">
+        <v>38</v>
+      </c>
+      <c r="K23" t="s">
+        <v>42</v>
+      </c>
+      <c r="L23" t="s">
+        <v>68</v>
+      </c>
+      <c r="M23" t="s">
+        <v>69</v>
+      </c>
+      <c r="N23" t="s">
+        <v>57</v>
+      </c>
+      <c r="O23" t="s">
+        <v>70</v>
+      </c>
+      <c r="P23">
         <v>10</v>
       </c>
     </row>
@@ -1409,23 +1845,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A898AA9E-6EE8-44A9-9DEF-7D9FA314DBCA}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1448,7 +1884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1471,7 +1907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1494,7 +1930,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1517,7 +1953,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1540,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1563,7 +1999,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1586,7 +2022,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1609,7 +2045,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1632,7 +2068,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1655,7 +2091,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1678,7 +2114,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1701,7 +2137,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1724,7 +2160,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1747,7 +2183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1770,7 +2206,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1793,7 +2229,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1824,23 +2260,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E73D97-BC3F-49A1-B8F4-F095906B505B}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1863,7 +2299,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1886,7 +2322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1909,7 +2345,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1932,7 +2368,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1955,7 +2391,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1978,7 +2414,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2001,7 +2437,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2024,7 +2460,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2047,7 +2483,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2070,7 +2506,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2093,7 +2529,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -2116,7 +2552,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2139,7 +2575,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2162,7 +2598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2185,7 +2621,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2208,7 +2644,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2239,23 +2675,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A57D4CE-8BDF-4BD2-8CFC-2B5D7CFE333B}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2278,7 +2714,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2301,7 +2737,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2324,7 +2760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2347,7 +2783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2370,7 +2806,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2393,7 +2829,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2416,7 +2852,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2439,7 +2875,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2462,7 +2898,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2485,7 +2921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2508,7 +2944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -2531,7 +2967,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2554,7 +2990,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2577,7 +3013,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2600,7 +3036,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2623,7 +3059,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>

--- a/MCDA_Ratings_Werkspoor.xlsx
+++ b/MCDA_Ratings_Werkspoor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Amit/Documents/GitHub/Structural-group-5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D85B58D-B248-134F-ACDE-2F7918FE05F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C438EE-28AC-114A-8E4F-E0AEE8DB3926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2320" yWindow="500" windowWidth="26480" windowHeight="16060" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="78">
   <si>
     <t>MCDA Gold Coast Design Alternatives</t>
   </si>
@@ -249,6 +249,27 @@
   </si>
   <si>
     <t>existing transit infrastructure will need to be renovated to accommodate increased demand, can potentially affect visual appeal of area</t>
+  </si>
+  <si>
+    <t>Werkspoor bridge</t>
+  </si>
+  <si>
+    <t>Criteria Weight</t>
+  </si>
+  <si>
+    <t>Werkppoor bridge</t>
+  </si>
+  <si>
+    <t>alternate rail lines running during revovation of demka bridge</t>
+  </si>
+  <si>
+    <t>will increase line capacity after demka is renovated</t>
+  </si>
+  <si>
+    <t>lots of steel required, though not as much as the truss bridge</t>
+  </si>
+  <si>
+    <t>very pretty bridge</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E21EC2-64DE-445B-8154-60469756B239}">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
@@ -1121,14 +1142,15 @@
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5" customWidth="1"/>
-    <col min="13" max="13" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.1640625" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="17" max="17" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1136,7 +1158,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1165,22 +1187,25 @@
         <v>2</v>
       </c>
       <c r="L2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" t="s">
         <v>36</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>37</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>40</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>41</v>
       </c>
-      <c r="P2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1212,19 +1237,22 @@
         <v>100</v>
       </c>
       <c r="M3">
+        <v>100</v>
+      </c>
+      <c r="N3">
         <v>80</v>
       </c>
-      <c r="N3">
-        <v>100</v>
-      </c>
       <c r="O3">
+        <v>100</v>
+      </c>
+      <c r="P3">
         <v>40</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1253,22 +1281,25 @@
         <v>17</v>
       </c>
       <c r="L4">
+        <v>90</v>
+      </c>
+      <c r="M4">
         <v>60</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>80</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>90</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>70</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1297,22 +1328,25 @@
         <v>39</v>
       </c>
       <c r="L5">
+        <v>50</v>
+      </c>
+      <c r="M5">
         <v>40</v>
       </c>
-      <c r="M5">
-        <v>100</v>
-      </c>
       <c r="N5">
+        <v>100</v>
+      </c>
+      <c r="O5">
         <v>50</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>30</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1344,19 +1378,22 @@
         <v>80</v>
       </c>
       <c r="M6">
+        <v>80</v>
+      </c>
+      <c r="N6">
         <v>10</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>80</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>30</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1385,22 +1422,25 @@
         <v>22</v>
       </c>
       <c r="L7">
+        <v>60</v>
+      </c>
+      <c r="M7">
         <v>50</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>90</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>50</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>60</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1429,22 +1469,25 @@
         <v>42</v>
       </c>
       <c r="L8">
+        <v>70</v>
+      </c>
+      <c r="M8">
         <v>80</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>95</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>50</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>60</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1467,7 +1510,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1490,7 +1533,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1513,7 +1556,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1536,7 +1579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1559,7 +1602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1581,11 +1624,11 @@
       <c r="G14" t="s">
         <v>29</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1608,7 +1651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1634,7 +1677,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1663,22 +1706,25 @@
         <v>2</v>
       </c>
       <c r="L17" t="s">
+        <v>73</v>
+      </c>
+      <c r="M17" t="s">
         <v>36</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>37</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>40</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>41</v>
       </c>
-      <c r="P17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1707,22 +1753,25 @@
         <v>35</v>
       </c>
       <c r="L18" t="s">
+        <v>74</v>
+      </c>
+      <c r="M18" t="s">
         <v>46</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>44</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>45</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>52</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="J19" t="s">
         <v>38</v>
       </c>
@@ -1730,22 +1779,25 @@
         <v>17</v>
       </c>
       <c r="L19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M19" t="s">
         <v>47</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>49</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>51</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>53</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="J20" t="s">
         <v>38</v>
       </c>
@@ -1753,22 +1805,25 @@
         <v>39</v>
       </c>
       <c r="L20" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20" t="s">
         <v>60</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>61</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>62</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>63</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="J21" t="s">
         <v>38</v>
       </c>
@@ -1776,22 +1831,25 @@
         <v>54</v>
       </c>
       <c r="L21" t="s">
+        <v>75</v>
+      </c>
+      <c r="M21" t="s">
         <v>55</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>56</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>58</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>59</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="J22" t="s">
         <v>38</v>
       </c>
@@ -1799,22 +1857,25 @@
         <v>22</v>
       </c>
       <c r="L22" t="s">
+        <v>76</v>
+      </c>
+      <c r="M22" t="s">
         <v>64</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>65</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>66</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>67</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="J23" t="s">
         <v>38</v>
       </c>
@@ -1822,18 +1883,21 @@
         <v>42</v>
       </c>
       <c r="L23" t="s">
+        <v>77</v>
+      </c>
+      <c r="M23" t="s">
         <v>68</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>69</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>57</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>70</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>10</v>
       </c>
     </row>

--- a/MCDA_Ratings_Werkspoor.xlsx
+++ b/MCDA_Ratings_Werkspoor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Structural-group-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tvanr\OneDrive\Documenten\BASE\Structural-group-5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB86BD7-3DA8-4669-A059-008E3730C985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB3E9E6-0310-49D2-A9B2-0AEE70508CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Nature by Prajwal" sheetId="4" r:id="rId1"/>
@@ -18,17 +18,25 @@
     <sheet name="Government by Thijmen" sheetId="2" r:id="rId3"/>
     <sheet name="Citizen by Amit" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="51">
   <si>
     <t>MCDA Gold Coast Design Alternatives</t>
   </si>
@@ -133,13 +141,64 @@
   </si>
   <si>
     <t>Tourist Sector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCDA government </t>
+  </si>
+  <si>
+    <t>Tunnel</t>
+  </si>
+  <si>
+    <t>Dont widen the river</t>
+  </si>
+  <si>
+    <t>Truss bridgte</t>
+  </si>
+  <si>
+    <t>construct a bridgte somewhere else</t>
+  </si>
+  <si>
+    <t>Initial cost</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Durability</t>
+  </si>
+  <si>
+    <t>life cycle costs</t>
+  </si>
+  <si>
+    <t>fit within surrounding</t>
+  </si>
+  <si>
+    <t>Climate adaption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emissions </t>
+  </si>
+  <si>
+    <t>Accessibility(transport)</t>
+  </si>
+  <si>
+    <t>constructability</t>
+  </si>
+  <si>
+    <t>Werkspoorbridge</t>
+  </si>
+  <si>
+    <t>Criteriaweight</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -616,8 +675,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -644,24 +704,24 @@
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Berekening" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Controlecel" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Gekoppelde cel" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Goed" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Invoer" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Kop 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Kop 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Kop 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Kop 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Neutraal" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Notitie" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Ongeldig" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Titel" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Totaal" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Uitvoer" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Verklarende tekst" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Waarschuwingstekst" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -994,23 +1054,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E21EC2-64DE-445B-8154-60469756B239}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.9140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1033,7 +1093,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1056,7 +1116,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1079,7 +1139,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1102,7 +1162,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1125,7 +1185,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1148,7 +1208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1171,7 +1231,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1194,7 +1254,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1217,7 +1277,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1240,7 +1300,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1263,7 +1323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1286,7 +1346,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1309,7 +1369,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1332,7 +1392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1355,7 +1415,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1378,7 +1438,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1409,23 +1469,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A898AA9E-6EE8-44A9-9DEF-7D9FA314DBCA}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.9140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1448,7 +1508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1471,7 +1531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1494,7 +1554,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1517,7 +1577,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1540,7 +1600,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1563,7 +1623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1586,7 +1646,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1609,7 +1669,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1632,7 +1692,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1655,7 +1715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1678,7 +1738,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1701,7 +1761,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1724,7 +1784,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1747,7 +1807,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1770,7 +1830,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1793,7 +1853,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1823,439 +1883,302 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E73D97-BC3F-49A1-B8F4-F095906B505B}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.9140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9">
+        <v>7</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F10">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="F11">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>80</v>
-      </c>
-      <c r="D3">
-        <v>100</v>
-      </c>
-      <c r="E3">
+      <c r="G11">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
         <v>10</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>25</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>80</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>50</v>
-      </c>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>80</v>
-      </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>75</v>
-      </c>
-      <c r="F7">
-        <v>75</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>80</v>
-      </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>70</v>
-      </c>
-      <c r="D10">
-        <v>100</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11">
-        <v>100</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>75</v>
-      </c>
-      <c r="F11">
-        <v>75</v>
-      </c>
-      <c r="G11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12">
-        <v>80</v>
-      </c>
       <c r="D12">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13">
-        <v>100</v>
-      </c>
-      <c r="D13">
-        <v>50</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>100</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15">
-        <v>100</v>
-      </c>
-      <c r="D15">
-        <v>90</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>100</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-      <c r="G16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>80</v>
-      </c>
-      <c r="F17">
-        <v>100</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18">
-        <v>70</v>
-      </c>
-      <c r="D18">
-        <v>100</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="G12">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A57D4CE-8BDF-4BD2-8CFC-2B5D7CFE333B}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.9140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2278,7 +2201,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2301,7 +2224,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2324,7 +2247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2347,7 +2270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2370,7 +2293,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2393,7 +2316,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2416,7 +2339,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2439,7 +2362,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2462,7 +2385,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2485,7 +2408,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2508,7 +2431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -2531,7 +2454,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2554,7 +2477,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2577,7 +2500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2600,7 +2523,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2623,7 +2546,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2644,6 +2567,20 @@
       </c>
       <c r="G18" t="s">
         <v>10</v>
+      </c>
+      <c r="H18" t="str">
+        <f>G18</f>
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G19" s="1">
+        <f>SUM(G3:G18)</f>
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <f>SUM(H3:H18)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/MCDA_Ratings_Werkspoor.xlsx
+++ b/MCDA_Ratings_Werkspoor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Amit/Documents/GitHub/Structural-group-5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tvanr\OneDrive\Documenten\BASE\Structural-group-5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C438EE-28AC-114A-8E4F-E0AEE8DB3926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0A7A8C-FE67-4371-A516-884337DEC406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2320" yWindow="500" windowWidth="26480" windowHeight="16060" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Nature by Prajwal" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="94">
   <si>
     <t>MCDA Gold Coast Design Alternatives</t>
   </si>
@@ -270,6 +270,54 @@
   </si>
   <si>
     <t>very pretty bridge</t>
+  </si>
+  <si>
+    <t>Criterium</t>
+  </si>
+  <si>
+    <t>Tunnel</t>
+  </si>
+  <si>
+    <t>Don't widen river</t>
+  </si>
+  <si>
+    <t>Truss bridge</t>
+  </si>
+  <si>
+    <t>Initial cost</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Durability</t>
+  </si>
+  <si>
+    <t>Life cycle costs</t>
+  </si>
+  <si>
+    <t>Fit within surrounding</t>
+  </si>
+  <si>
+    <t>Climate adaptation</t>
+  </si>
+  <si>
+    <t>Emissions</t>
+  </si>
+  <si>
+    <t>Accessibility (transport)</t>
+  </si>
+  <si>
+    <t>Constructability</t>
+  </si>
+  <si>
+    <t>Bridge somewhere sle</t>
+  </si>
+  <si>
+    <t>Werspoorbridge</t>
+  </si>
+  <si>
+    <t>Criteriaweight</t>
   </si>
 </sst>
 </file>
@@ -753,8 +801,17 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -781,24 +838,24 @@
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Berekening" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Controlecel" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Gekoppelde cel" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Goed" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Invoer" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Kop 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Kop 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Kop 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Kop 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Neutraal" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Notitie" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Ongeldig" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Titel" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Totaal" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Uitvoer" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Verklarende tekst" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Waarschuwingstekst" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1131,26 +1188,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E21EC2-64DE-445B-8154-60469756B239}">
   <dimension ref="A1:Q23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.1640625" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" customWidth="1"/>
     <col min="15" max="15" width="10.6640625" customWidth="1"/>
     <col min="16" max="16" width="15" customWidth="1"/>
     <col min="17" max="17" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1158,7 +1215,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1205,7 +1262,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1252,7 +1309,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1299,7 +1356,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1346,7 +1403,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1393,7 +1450,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1440,7 +1497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1487,7 +1544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1510,7 +1567,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1533,7 +1590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1556,7 +1613,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1579,7 +1636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1602,7 +1659,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1628,7 +1685,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1651,7 +1708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1677,7 +1734,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1724,7 +1781,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1771,7 +1828,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J19" t="s">
         <v>38</v>
       </c>
@@ -1797,7 +1854,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J20" t="s">
         <v>38</v>
       </c>
@@ -1823,7 +1880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J21" t="s">
         <v>38</v>
       </c>
@@ -1849,7 +1906,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J22" t="s">
         <v>38</v>
       </c>
@@ -1875,7 +1932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J23" t="s">
         <v>38</v>
       </c>
@@ -1909,23 +1966,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A898AA9E-6EE8-44A9-9DEF-7D9FA314DBCA}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1948,7 +2005,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1971,7 +2028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1994,7 +2051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2017,7 +2074,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2040,7 +2097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2063,7 +2120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2086,7 +2143,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2109,7 +2166,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2132,7 +2189,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2155,7 +2212,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2178,7 +2235,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -2201,7 +2258,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2224,7 +2281,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2247,7 +2304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2270,7 +2327,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2293,7 +2350,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2323,412 +2380,275 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E73D97-BC3F-49A1-B8F4-F095906B505B}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A2:G13"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2">
+        <v>6</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2">
+        <v>7</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="2">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="2">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>7</v>
+      </c>
+      <c r="F7" s="2">
+        <v>7</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="2">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2">
+        <v>6</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2">
+        <v>7</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2">
+        <v>5</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="2">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2">
+        <v>6</v>
+      </c>
+      <c r="F11" s="2">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="2">
+        <v>3</v>
+      </c>
+      <c r="C12" s="2">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2">
+        <v>6</v>
+      </c>
+      <c r="E12" s="2">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <f>SUM(G3:G12)</f>
         <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>80</v>
-      </c>
-      <c r="D3">
-        <v>100</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>25</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>80</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>50</v>
-      </c>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>80</v>
-      </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>75</v>
-      </c>
-      <c r="F7">
-        <v>75</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>80</v>
-      </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>70</v>
-      </c>
-      <c r="D10">
-        <v>100</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11">
-        <v>100</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>75</v>
-      </c>
-      <c r="F11">
-        <v>75</v>
-      </c>
-      <c r="G11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12">
-        <v>80</v>
-      </c>
-      <c r="D12">
-        <v>100</v>
-      </c>
-      <c r="E12">
-        <v>20</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13">
-        <v>100</v>
-      </c>
-      <c r="D13">
-        <v>50</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>100</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15">
-        <v>100</v>
-      </c>
-      <c r="D15">
-        <v>90</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>100</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-      <c r="G16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>80</v>
-      </c>
-      <c r="F17">
-        <v>100</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18">
-        <v>70</v>
-      </c>
-      <c r="D18">
-        <v>100</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2739,23 +2659,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A57D4CE-8BDF-4BD2-8CFC-2B5D7CFE333B}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2778,7 +2698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2801,7 +2721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2824,7 +2744,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2847,7 +2767,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2870,7 +2790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2893,7 +2813,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2916,7 +2836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2939,7 +2859,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2962,7 +2882,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2985,7 +2905,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -3008,7 +2928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -3031,7 +2951,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3054,7 +2974,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -3077,7 +2997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3100,7 +3020,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -3123,7 +3043,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>

--- a/MCDA_Ratings_Werkspoor.xlsx
+++ b/MCDA_Ratings_Werkspoor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tvanr\OneDrive\Documenten\BASE\Structural-group-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Structural-group-5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0A7A8C-FE67-4371-A516-884337DEC406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E414F33-32B8-415C-A027-64029D1FDD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Nature by Prajwal" sheetId="4" r:id="rId1"/>
@@ -27,16 +27,152 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="G27" authorId="0" shapeId="0" xr:uid="{4DDA345A-73D9-48AC-873E-EE36739842E0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Initial cost might impac the series of financial priorities of government leading to less priority for climate related issues
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G28" authorId="0" shapeId="0" xr:uid="{F2F2D73D-0340-40E8-AE09-416FAED45B6F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Long term structural benifits results into lower harm to environment and higher cost benifit over time
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G29" authorId="0" shapeId="0" xr:uid="{A0D79046-A410-439D-8790-B6C1F99BB253}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Greenery and presence of vegetation
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G30" authorId="0" shapeId="0" xr:uid="{ADCE6BF6-FD02-45D6-A3D8-860D599C1F25}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Should be able to function with the climate change
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G31" authorId="0" shapeId="0" xr:uid="{47E5CF1C-56B5-4380-B128-4187BD8C5B1B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Carbon emission during construction
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="99">
   <si>
     <t>MCDA Gold Coast Design Alternatives</t>
   </si>
@@ -318,13 +454,28 @@
   </si>
   <si>
     <t>Criteriaweight</t>
+  </si>
+  <si>
+    <t>Bridge somewhere else</t>
+  </si>
+  <si>
+    <t>Aquatic life</t>
+  </si>
+  <si>
+    <t>Emissions during construction</t>
+  </si>
+  <si>
+    <t>Fit within surrounding (In terms of vegetation)</t>
+  </si>
+  <si>
+    <t>Energy use during lifecycle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,6 +609,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="33">
@@ -838,24 +1002,24 @@
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Berekening" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Controlecel" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Gekoppelde cel" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Goed" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Invoer" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Kop 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Kop 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Kop 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Kop 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Neutraal" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Notitie" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Ongeldig" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
-    <cellStyle name="Titel" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Totaal" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Uitvoer" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Verklarende tekst" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Waarschuwingstekst" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1186,28 +1350,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E21EC2-64DE-445B-8154-60469756B239}">
-  <dimension ref="A1:Q23"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E21EC2-64DE-445B-8154-60469756B239}">
+  <dimension ref="A1:Q34"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.08203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.08203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.4140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.109375" customWidth="1"/>
-    <col min="14" max="14" width="12.77734375" customWidth="1"/>
+    <col min="13" max="13" width="8.08203125" customWidth="1"/>
+    <col min="14" max="14" width="12.75" customWidth="1"/>
     <col min="15" max="15" width="10.6640625" customWidth="1"/>
     <col min="16" max="16" width="15" customWidth="1"/>
     <col min="17" max="17" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="14.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1215,7 +1379,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="14.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1262,7 +1426,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="14.4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1309,7 +1473,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="14.4">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1356,7 +1520,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="14.4">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1403,7 +1567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="14.4">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1450,7 +1614,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="14.4">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1497,7 +1661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="14.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1544,7 +1708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="14.4">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1567,7 +1731,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="14.4">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1590,7 +1754,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="14.4">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1613,7 +1777,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="14.4">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1636,7 +1800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="14.4">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1659,7 +1823,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="14.4">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1685,7 +1849,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="14.4">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1708,7 +1872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="14.4">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1734,7 +1898,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="14.4">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1781,7 +1945,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="14.4">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1828,7 +1992,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="14.4">
       <c r="J19" t="s">
         <v>38</v>
       </c>
@@ -1854,7 +2018,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="14.4">
       <c r="J20" t="s">
         <v>38</v>
       </c>
@@ -1880,7 +2044,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="14.4">
       <c r="J21" t="s">
         <v>38</v>
       </c>
@@ -1906,7 +2070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="14.4">
       <c r="J22" t="s">
         <v>38</v>
       </c>
@@ -1932,7 +2096,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="14.4">
       <c r="J23" t="s">
         <v>38</v>
       </c>
@@ -1958,31 +2122,222 @@
         <v>10</v>
       </c>
     </row>
+    <row r="26" spans="1:17" ht="28">
+      <c r="A26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2">
+        <v>5</v>
+      </c>
+      <c r="E27" s="2">
+        <v>5</v>
+      </c>
+      <c r="F27" s="2">
+        <v>5</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="2">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2">
+        <v>8</v>
+      </c>
+      <c r="F28" s="2">
+        <v>8</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="28">
+      <c r="A29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="2">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2">
+        <v>10</v>
+      </c>
+      <c r="D29" s="2">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2">
+        <v>5</v>
+      </c>
+      <c r="F29" s="2">
+        <v>8</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="2">
+        <v>10</v>
+      </c>
+      <c r="C30" s="2">
+        <v>3</v>
+      </c>
+      <c r="D30" s="2">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2">
+        <v>8</v>
+      </c>
+      <c r="F30" s="2">
+        <v>8</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2</v>
+      </c>
+      <c r="C31" s="2">
+        <v>10</v>
+      </c>
+      <c r="D31" s="2">
+        <v>5</v>
+      </c>
+      <c r="E31" s="2">
+        <v>5</v>
+      </c>
+      <c r="F31" s="2">
+        <v>7</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2">
+        <v>10</v>
+      </c>
+      <c r="D32" s="2">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2">
+        <v>8</v>
+      </c>
+      <c r="F32" s="2">
+        <v>8</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="2">
+        <v>9</v>
+      </c>
+      <c r="C33" s="2">
+        <v>10</v>
+      </c>
+      <c r="D33" s="2">
+        <v>5</v>
+      </c>
+      <c r="E33" s="2">
+        <v>5</v>
+      </c>
+      <c r="F33" s="2">
+        <v>5</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="G34">
+        <f>SUM(G27:G33)</f>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A898AA9E-6EE8-44A9-9DEF-7D9FA314DBCA}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.08203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2005,7 +2360,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2028,7 +2383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2051,7 +2406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2074,7 +2429,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2097,7 +2452,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2120,7 +2475,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2143,7 +2498,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2166,7 +2521,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2189,7 +2544,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2212,7 +2567,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2235,7 +2590,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -2258,7 +2613,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2281,7 +2636,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2304,7 +2659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2327,7 +2682,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2350,7 +2705,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2381,18 +2736,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E73D97-BC3F-49A1-B8F4-F095906B505B}">
   <dimension ref="A2:G13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.08203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.58203125" customWidth="1"/>
     <col min="6" max="6" width="19.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>78</v>
       </c>
@@ -2415,7 +2770,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
         <v>82</v>
       </c>
@@ -2438,7 +2793,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
@@ -2461,7 +2816,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="3" t="s">
         <v>83</v>
       </c>
@@ -2484,7 +2839,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="3" t="s">
         <v>84</v>
       </c>
@@ -2507,7 +2862,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="3" t="s">
         <v>85</v>
       </c>
@@ -2530,7 +2885,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
         <v>86</v>
       </c>
@@ -2553,7 +2908,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
         <v>87</v>
       </c>
@@ -2576,7 +2931,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
         <v>88</v>
       </c>
@@ -2599,7 +2954,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
         <v>89</v>
       </c>
@@ -2622,7 +2977,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" s="3" t="s">
         <v>90</v>
       </c>
@@ -2645,7 +3000,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="G13">
         <f>SUM(G3:G12)</f>
         <v>1</v>
@@ -2659,23 +3014,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A57D4CE-8BDF-4BD2-8CFC-2B5D7CFE333B}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.08203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2698,7 +3053,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2721,7 +3076,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2744,7 +3099,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2767,7 +3122,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2790,7 +3145,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2813,7 +3168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2836,7 +3191,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2859,7 +3214,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2882,7 +3237,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2905,7 +3260,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2928,7 +3283,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -2951,7 +3306,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2974,7 +3329,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2997,7 +3352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3020,7 +3375,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -3043,7 +3398,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>34</v>
       </c>

--- a/MCDA_Ratings_Werkspoor.xlsx
+++ b/MCDA_Ratings_Werkspoor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Structural-group-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1378a22be3563c43/Delft/Interdiscip/Structural-group-5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E414F33-32B8-415C-A027-64029D1FDD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{0E414F33-32B8-415C-A027-64029D1FDD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F60C315-C488-43DF-915C-A9C9A258E2DB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Nature by Prajwal" sheetId="4" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -172,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="99">
   <si>
     <t>MCDA Gold Coast Design Alternatives</t>
   </si>
@@ -475,7 +472,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -967,13 +964,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1002,24 +999,24 @@
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Berekening" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Controlecel" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Gekoppelde cel" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Goed" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Invoer" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Kop 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Kop 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Kop 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Kop 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Neutraal" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Notitie" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Ongeldig" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Titel" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Totaal" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Uitvoer" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Verklarende tekst" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Waarschuwingstekst" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1352,26 +1349,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E21EC2-64DE-445B-8154-60469756B239}">
   <dimension ref="A1:Q34"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1640625" customWidth="1"/>
-    <col min="7" max="7" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.4140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.08203125" customWidth="1"/>
-    <col min="14" max="14" width="12.75" customWidth="1"/>
+    <col min="13" max="13" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" customWidth="1"/>
     <col min="15" max="15" width="10.6640625" customWidth="1"/>
     <col min="16" max="16" width="15" customWidth="1"/>
     <col min="17" max="17" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="14.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1379,7 +1376,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="14.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1426,7 +1423,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="14.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1473,7 +1470,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="14.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1520,7 +1517,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="14.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1567,7 +1564,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="14.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1614,7 +1611,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="14.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1661,7 +1658,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="14.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1708,7 +1705,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="14.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1731,7 +1728,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="14.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1754,7 +1751,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="14.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1777,7 +1774,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="14.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1800,7 +1797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="14.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1823,7 +1820,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="14.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1849,7 +1846,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="14.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1872,7 +1869,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="14.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1898,7 +1895,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="14.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1945,7 +1942,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="14.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1992,7 +1989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="14.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J19" t="s">
         <v>38</v>
       </c>
@@ -2018,7 +2015,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="14.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J20" t="s">
         <v>38</v>
       </c>
@@ -2044,7 +2041,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="14.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J21" t="s">
         <v>38</v>
       </c>
@@ -2070,7 +2067,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="14.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J22" t="s">
         <v>38</v>
       </c>
@@ -2096,7 +2093,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="14.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J23" t="s">
         <v>38</v>
       </c>
@@ -2122,7 +2119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="28">
+    <row r="26" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>78</v>
       </c>
@@ -2145,7 +2142,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>82</v>
       </c>
@@ -2168,7 +2165,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>84</v>
       </c>
@@ -2191,7 +2188,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="28">
+    <row r="29" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>97</v>
       </c>
@@ -2214,7 +2211,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>87</v>
       </c>
@@ -2237,7 +2234,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>96</v>
       </c>
@@ -2260,7 +2257,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>98</v>
       </c>
@@ -2283,7 +2280,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>95</v>
       </c>
@@ -2306,7 +2303,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G34">
         <f>SUM(G27:G33)</f>
         <v>0.99999999999999989</v>
@@ -2320,412 +2317,137 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A898AA9E-6EE8-44A9-9DEF-7D9FA314DBCA}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14"/>
+  <dimension ref="B4:H9"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.4140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="4" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2">
+        <v>7</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="2">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2">
+        <v>8</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="2">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E7" s="2">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2">
+        <v>9</v>
+      </c>
+      <c r="G7" s="2">
+        <v>8</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="2">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E8" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>80</v>
-      </c>
-      <c r="D3">
-        <v>100</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>25</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>80</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>50</v>
-      </c>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>80</v>
-      </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>75</v>
-      </c>
-      <c r="F7">
-        <v>75</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>80</v>
-      </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>70</v>
-      </c>
-      <c r="D10">
-        <v>100</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11">
-        <v>100</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>75</v>
-      </c>
-      <c r="F11">
-        <v>75</v>
-      </c>
-      <c r="G11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12">
-        <v>80</v>
-      </c>
-      <c r="D12">
-        <v>100</v>
-      </c>
-      <c r="E12">
-        <v>20</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13">
-        <v>100</v>
-      </c>
-      <c r="D13">
-        <v>50</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>100</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15">
-        <v>100</v>
-      </c>
-      <c r="D15">
-        <v>90</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>100</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-      <c r="G16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>80</v>
-      </c>
-      <c r="F17">
-        <v>100</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18">
-        <v>70</v>
-      </c>
-      <c r="D18">
-        <v>100</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
-        <v>10</v>
+      <c r="F8" s="2">
+        <v>7</v>
+      </c>
+      <c r="G8" s="2">
+        <v>7</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <f>SUM(H5:H8)</f>
+        <v>1.0000000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -2736,18 +2458,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E73D97-BC3F-49A1-B8F4-F095906B505B}">
   <dimension ref="A2:G13"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.58203125" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" customWidth="1"/>
     <col min="6" max="6" width="19.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>78</v>
       </c>
@@ -2770,7 +2492,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>82</v>
       </c>
@@ -2793,7 +2515,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
@@ -2816,7 +2538,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>83</v>
       </c>
@@ -2839,7 +2561,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>84</v>
       </c>
@@ -2862,7 +2584,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>85</v>
       </c>
@@ -2885,7 +2607,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>86</v>
       </c>
@@ -2908,7 +2630,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>87</v>
       </c>
@@ -2931,7 +2653,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>88</v>
       </c>
@@ -2954,7 +2676,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>89</v>
       </c>
@@ -2977,7 +2699,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>90</v>
       </c>
@@ -3000,7 +2722,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G13">
         <f>SUM(G3:G12)</f>
         <v>1</v>
@@ -3014,23 +2736,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A57D4CE-8BDF-4BD2-8CFC-2B5D7CFE333B}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.4140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3053,7 +2775,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -3076,7 +2798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3099,7 +2821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3122,7 +2844,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3145,7 +2867,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -3168,7 +2890,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -3191,7 +2913,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -3214,7 +2936,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -3237,7 +2959,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -3260,7 +2982,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -3283,7 +3005,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -3306,7 +3028,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3329,7 +3051,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -3352,7 +3074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3375,7 +3097,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -3398,7 +3120,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>

--- a/MCDA_Ratings_Werkspoor.xlsx
+++ b/MCDA_Ratings_Werkspoor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1378a22be3563c43/Delft/Interdiscip/Structural-group-5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{0E414F33-32B8-415C-A027-64029D1FDD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F60C315-C488-43DF-915C-A9C9A258E2DB}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{0E414F33-32B8-415C-A027-64029D1FDD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64129238-B0C8-4815-B1EE-7ECC4595E048}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
   </bookViews>
@@ -169,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="105">
   <si>
     <t>MCDA Gold Coast Design Alternatives</t>
   </si>
@@ -466,6 +466,24 @@
   </si>
   <si>
     <t>Energy use during lifecycle</t>
+  </si>
+  <si>
+    <t>Companies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety </t>
+  </si>
+  <si>
+    <t>If the structure is safe the comapnies can use it</t>
+  </si>
+  <si>
+    <t>Higher capicity equals more use</t>
+  </si>
+  <si>
+    <t>Less maintenance means more use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potential payments they need to make (help paying). </t>
   </si>
 </sst>
 </file>
@@ -2317,7 +2335,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A898AA9E-6EE8-44A9-9DEF-7D9FA314DBCA}">
-  <dimension ref="B4:H9"/>
+  <dimension ref="B2:H15"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
@@ -2329,6 +2347,11 @@
     <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+    </row>
     <row r="4" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>78</v>
@@ -2448,6 +2471,46 @@
       <c r="H9">
         <f>SUM(H5:H8)</f>
         <v>1.0000000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/MCDA_Ratings_Werkspoor.xlsx
+++ b/MCDA_Ratings_Werkspoor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1378a22be3563c43/Delft/Interdiscip/Structural-group-5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Amit/Documents/GitHub/Structural-group-5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{0E414F33-32B8-415C-A027-64029D1FDD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64129238-B0C8-4815-B1EE-7ECC4595E048}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF54290F-D2E7-264E-ADFB-2FD300AD9917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" activeTab="3" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Nature by Prajwal" sheetId="4" r:id="rId1"/>
@@ -47,7 +47,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -56,7 +56,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Initial cost might impac the series of financial priorities of government leading to less priority for climate related issues
@@ -72,7 +72,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -81,7 +81,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Long term structural benifits results into lower harm to environment and higher cost benifit over time
@@ -97,7 +97,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -106,7 +106,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Greenery and presence of vegetation
@@ -122,7 +122,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -131,7 +131,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Should be able to function with the climate change
@@ -147,7 +147,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -156,7 +156,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Carbon emission during construction
@@ -169,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="105">
   <si>
     <t>MCDA Gold Coast Design Alternatives</t>
   </si>
@@ -629,14 +629,14 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1017,24 +1017,24 @@
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Berekening" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Controlecel" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Gekoppelde cel" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Goed" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Invoer" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Kop 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Kop 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Kop 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Kop 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Neutraal" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Notitie" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Ongeldig" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
-    <cellStyle name="Titel" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Totaal" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Uitvoer" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Verklarende tekst" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Waarschuwingstekst" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1050,7 +1050,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1366,35 +1366,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E21EC2-64DE-445B-8154-60469756B239}">
-  <dimension ref="A1:Q34"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.109375" customWidth="1"/>
-    <col min="14" max="14" width="12.77734375" customWidth="1"/>
+    <col min="13" max="13" width="8.1640625" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
     <col min="15" max="15" width="10.6640625" customWidth="1"/>
     <col min="16" max="16" width="15" customWidth="1"/>
     <col min="17" max="17" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="J1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1416,32 +1413,8 @@
       <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>2</v>
-      </c>
-      <c r="L2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1463,32 +1436,8 @@
       <c r="G3" t="s">
         <v>10</v>
       </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3">
-        <v>100</v>
-      </c>
-      <c r="M3">
-        <v>100</v>
-      </c>
-      <c r="N3">
-        <v>80</v>
-      </c>
-      <c r="O3">
-        <v>100</v>
-      </c>
-      <c r="P3">
-        <v>40</v>
-      </c>
-      <c r="Q3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1510,32 +1459,8 @@
       <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="J4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4">
-        <v>90</v>
-      </c>
-      <c r="M4">
-        <v>60</v>
-      </c>
-      <c r="N4">
-        <v>80</v>
-      </c>
-      <c r="O4">
-        <v>90</v>
-      </c>
-      <c r="P4">
-        <v>70</v>
-      </c>
-      <c r="Q4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1557,32 +1482,8 @@
       <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="J5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5">
-        <v>50</v>
-      </c>
-      <c r="M5">
-        <v>40</v>
-      </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
-      <c r="O5">
-        <v>50</v>
-      </c>
-      <c r="P5">
-        <v>30</v>
-      </c>
-      <c r="Q5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1604,32 +1505,8 @@
       <c r="G6" t="s">
         <v>16</v>
       </c>
-      <c r="J6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6">
-        <v>80</v>
-      </c>
-      <c r="M6">
-        <v>80</v>
-      </c>
-      <c r="N6">
-        <v>10</v>
-      </c>
-      <c r="O6">
-        <v>80</v>
-      </c>
-      <c r="P6">
-        <v>30</v>
-      </c>
-      <c r="Q6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1651,32 +1528,8 @@
       <c r="G7" t="s">
         <v>18</v>
       </c>
-      <c r="J7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7">
-        <v>60</v>
-      </c>
-      <c r="M7">
-        <v>50</v>
-      </c>
-      <c r="N7">
-        <v>90</v>
-      </c>
-      <c r="O7">
-        <v>50</v>
-      </c>
-      <c r="P7">
-        <v>60</v>
-      </c>
-      <c r="Q7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1698,32 +1551,8 @@
       <c r="G8" t="s">
         <v>21</v>
       </c>
-      <c r="J8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" t="s">
-        <v>42</v>
-      </c>
-      <c r="L8">
-        <v>70</v>
-      </c>
-      <c r="M8">
-        <v>80</v>
-      </c>
-      <c r="N8">
-        <v>95</v>
-      </c>
-      <c r="O8">
-        <v>50</v>
-      </c>
-      <c r="P8">
-        <v>60</v>
-      </c>
-      <c r="Q8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1746,7 +1575,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1769,7 +1598,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1792,7 +1621,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1815,7 +1644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1838,7 +1667,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1860,11 +1689,8 @@
       <c r="G14" t="s">
         <v>29</v>
       </c>
-      <c r="N14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1887,7 +1713,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1909,11 +1735,8 @@
       <c r="G16" t="s">
         <v>33</v>
       </c>
-      <c r="J16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1935,32 +1758,8 @@
       <c r="G17" t="s">
         <v>33</v>
       </c>
-      <c r="J17" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" t="s">
-        <v>2</v>
-      </c>
-      <c r="L17" t="s">
-        <v>73</v>
-      </c>
-      <c r="M17" t="s">
-        <v>36</v>
-      </c>
-      <c r="N17" t="s">
-        <v>37</v>
-      </c>
-      <c r="O17" t="s">
-        <v>40</v>
-      </c>
-      <c r="P17" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1982,162 +1781,8 @@
       <c r="G18" t="s">
         <v>10</v>
       </c>
-      <c r="J18" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" t="s">
-        <v>35</v>
-      </c>
-      <c r="L18" t="s">
-        <v>74</v>
-      </c>
-      <c r="M18" t="s">
-        <v>46</v>
-      </c>
-      <c r="N18" t="s">
-        <v>44</v>
-      </c>
-      <c r="O18" t="s">
-        <v>45</v>
-      </c>
-      <c r="P18" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q18">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="J19" t="s">
-        <v>38</v>
-      </c>
-      <c r="K19" t="s">
-        <v>17</v>
-      </c>
-      <c r="L19" t="s">
-        <v>51</v>
-      </c>
-      <c r="M19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N19" t="s">
-        <v>49</v>
-      </c>
-      <c r="O19" t="s">
-        <v>51</v>
-      </c>
-      <c r="P19" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="J20" t="s">
-        <v>38</v>
-      </c>
-      <c r="K20" t="s">
-        <v>39</v>
-      </c>
-      <c r="L20" t="s">
-        <v>62</v>
-      </c>
-      <c r="M20" t="s">
-        <v>60</v>
-      </c>
-      <c r="N20" t="s">
-        <v>61</v>
-      </c>
-      <c r="O20" t="s">
-        <v>62</v>
-      </c>
-      <c r="P20" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q20">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="J21" t="s">
-        <v>38</v>
-      </c>
-      <c r="K21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L21" t="s">
-        <v>75</v>
-      </c>
-      <c r="M21" t="s">
-        <v>55</v>
-      </c>
-      <c r="N21" t="s">
-        <v>56</v>
-      </c>
-      <c r="O21" t="s">
-        <v>58</v>
-      </c>
-      <c r="P21" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q21">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="J22" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" t="s">
-        <v>22</v>
-      </c>
-      <c r="L22" t="s">
-        <v>76</v>
-      </c>
-      <c r="M22" t="s">
-        <v>64</v>
-      </c>
-      <c r="N22" t="s">
-        <v>65</v>
-      </c>
-      <c r="O22" t="s">
-        <v>66</v>
-      </c>
-      <c r="P22" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q22">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="J23" t="s">
-        <v>38</v>
-      </c>
-      <c r="K23" t="s">
-        <v>42</v>
-      </c>
-      <c r="L23" t="s">
-        <v>77</v>
-      </c>
-      <c r="M23" t="s">
-        <v>68</v>
-      </c>
-      <c r="N23" t="s">
-        <v>69</v>
-      </c>
-      <c r="O23" t="s">
-        <v>57</v>
-      </c>
-      <c r="P23" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>78</v>
       </c>
@@ -2160,7 +1805,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>82</v>
       </c>
@@ -2183,7 +1828,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>84</v>
       </c>
@@ -2206,7 +1851,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>97</v>
       </c>
@@ -2229,7 +1874,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>87</v>
       </c>
@@ -2252,7 +1897,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>96</v>
       </c>
@@ -2275,7 +1920,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>98</v>
       </c>
@@ -2298,7 +1943,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>95</v>
       </c>
@@ -2321,7 +1966,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G34">
         <f>SUM(G27:G33)</f>
         <v>0.99999999999999989</v>
@@ -2336,23 +1981,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A898AA9E-6EE8-44A9-9DEF-7D9FA314DBCA}">
   <dimension ref="B2:H15"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="48" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>78</v>
       </c>
@@ -2375,7 +2020,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
@@ -2398,7 +2043,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>83</v>
       </c>
@@ -2421,7 +2066,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>84</v>
       </c>
@@ -2444,7 +2089,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>85</v>
       </c>
@@ -2467,13 +2112,13 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H9">
         <f>SUM(H5:H8)</f>
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
         <v>99</v>
       </c>
@@ -2481,7 +2126,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
         <v>100</v>
       </c>
@@ -2489,7 +2134,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>83</v>
       </c>
@@ -2497,7 +2142,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
         <v>84</v>
       </c>
@@ -2505,7 +2150,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>85</v>
       </c>
@@ -2521,18 +2166,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E73D97-BC3F-49A1-B8F4-F095906B505B}">
   <dimension ref="A2:G13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
     <col min="6" max="6" width="19.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>78</v>
       </c>
@@ -2555,7 +2200,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>82</v>
       </c>
@@ -2578,7 +2223,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
@@ -2601,7 +2246,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>83</v>
       </c>
@@ -2624,7 +2269,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>84</v>
       </c>
@@ -2647,7 +2292,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>85</v>
       </c>
@@ -2670,7 +2315,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>86</v>
       </c>
@@ -2693,7 +2338,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>87</v>
       </c>
@@ -2716,7 +2361,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>88</v>
       </c>
@@ -2739,7 +2384,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>89</v>
       </c>
@@ -2762,7 +2407,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>90</v>
       </c>
@@ -2785,7 +2430,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G13">
         <f>SUM(G3:G12)</f>
         <v>1</v>
@@ -2798,411 +2443,394 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A57D4CE-8BDF-4BD2-8CFC-2B5D7CFE333B}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:I24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3">
+      <c r="D3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
         <v>80</v>
       </c>
-      <c r="D3">
+      <c r="G4">
         <v>100</v>
       </c>
-      <c r="E3">
+      <c r="H4">
+        <v>40</v>
+      </c>
+      <c r="I4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>90</v>
+      </c>
+      <c r="E5">
+        <v>60</v>
+      </c>
+      <c r="F5">
+        <v>80</v>
+      </c>
+      <c r="G5">
+        <v>90</v>
+      </c>
+      <c r="H5">
+        <v>70</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6">
+        <v>50</v>
+      </c>
+      <c r="E6">
+        <v>40</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>30</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7">
+        <v>80</v>
+      </c>
+      <c r="E7">
+        <v>80</v>
+      </c>
+      <c r="F7">
         <v>10</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="G7">
+        <v>80</v>
+      </c>
+      <c r="H7">
+        <v>30</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>60</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>90</v>
+      </c>
+      <c r="G8">
+        <v>50</v>
+      </c>
+      <c r="H8">
+        <v>60</v>
+      </c>
+      <c r="I8">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9">
+        <v>70</v>
+      </c>
+      <c r="E9">
+        <v>80</v>
+      </c>
+      <c r="F9">
+        <v>95</v>
+      </c>
+      <c r="G9">
+        <v>50</v>
+      </c>
+      <c r="H9">
+        <v>60</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" t="s">
+        <v>41</v>
+      </c>
+      <c r="I18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19">
         <v>25</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>80</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>50</v>
-      </c>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22">
         <v>15</v>
       </c>
-      <c r="C6">
-        <v>80</v>
-      </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>75</v>
-      </c>
-      <c r="F7">
-        <v>75</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>80</v>
-      </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
         <v>22</v>
       </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
+      <c r="D23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" t="s">
+        <v>57</v>
+      </c>
+      <c r="H24" t="s">
         <v>70</v>
       </c>
-      <c r="D10">
-        <v>100</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11">
-        <v>100</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>75</v>
-      </c>
-      <c r="F11">
-        <v>75</v>
-      </c>
-      <c r="G11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12">
-        <v>80</v>
-      </c>
-      <c r="D12">
-        <v>100</v>
-      </c>
-      <c r="E12">
-        <v>20</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13">
-        <v>100</v>
-      </c>
-      <c r="D13">
-        <v>50</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>100</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15">
-        <v>100</v>
-      </c>
-      <c r="D15">
-        <v>90</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>100</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-      <c r="G16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>80</v>
-      </c>
-      <c r="F17">
-        <v>100</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18">
-        <v>70</v>
-      </c>
-      <c r="D18">
-        <v>100</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="I24">
         <v>10</v>
       </c>
     </row>

--- a/MCDA_Ratings_Werkspoor.xlsx
+++ b/MCDA_Ratings_Werkspoor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Amit/Documents/GitHub/Structural-group-5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tvanr\OneDrive\Documenten\BASE\Structural-group-5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF54290F-D2E7-264E-ADFB-2FD300AD9917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE67D3D1-B646-4898-B29B-2E53D6602F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" activeTab="3" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26C83A51-C2F9-474F-A238-2673A092AE5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Nature by Prajwal" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <author>User</author>
   </authors>
   <commentList>
-    <comment ref="G27" authorId="0" shapeId="0" xr:uid="{4DDA345A-73D9-48AC-873E-EE36739842E0}">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{96A23AF6-C01B-4340-82EE-4FC31B42BE1C}">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G28" authorId="0" shapeId="0" xr:uid="{F2F2D73D-0340-40E8-AE09-416FAED45B6F}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{1ED16F4A-A91F-479D-9017-83DF0BC525F8}">
       <text>
         <r>
           <rPr>
@@ -85,6 +85,81 @@
           </rPr>
           <t xml:space="preserve">
 Long term structural benifits results into lower harm to environment and higher cost benifit over time
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{A2914ACA-EC0D-43D0-9307-4AD97076951F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Greenery and presence of vegetation
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{84CBA5FC-84B4-4500-9BBB-A7E5697561AE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Should be able to function with the climate change
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{92CA1BEF-88C5-4238-A515-F770774E4C70}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Carbon emission during construction
 </t>
         </r>
       </text>
@@ -139,40 +214,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="G31" authorId="0" shapeId="0" xr:uid="{47E5CF1C-56B5-4380-B128-4187BD8C5B1B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Carbon emission during construction
-</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="105">
-  <si>
-    <t>MCDA Gold Coast Design Alternatives</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="74">
   <si>
     <t>Stakeholder</t>
   </si>
@@ -180,100 +227,10 @@
     <t>Criteria</t>
   </si>
   <si>
-    <t>Artificial seaweed</t>
-  </si>
-  <si>
-    <t>Artificial reef</t>
-  </si>
-  <si>
-    <t>Breakwater</t>
-  </si>
-  <si>
-    <t>Groynes</t>
-  </si>
-  <si>
-    <t>Criteria_Weight</t>
-  </si>
-  <si>
-    <t>Gold Coast City Council</t>
-  </si>
-  <si>
-    <t>Beach use</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>Beach width and erosio control</t>
-  </si>
-  <si>
-    <t>0.13</t>
-  </si>
-  <si>
-    <t>Costs</t>
-  </si>
-  <si>
-    <t>0.20</t>
-  </si>
-  <si>
-    <t>Recreational opportunities</t>
-  </si>
-  <si>
-    <t>0.07</t>
-  </si>
-  <si>
     <t>Safety</t>
   </si>
   <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>Local Community</t>
-  </si>
-  <si>
-    <t>Beach width</t>
-  </si>
-  <si>
-    <t>0.35</t>
-  </si>
-  <si>
     <t>Environmental impact</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>0.10</t>
-  </si>
-  <si>
-    <t>Research Community</t>
-  </si>
-  <si>
-    <t>Erosion control</t>
-  </si>
-  <si>
-    <t>Wave creation</t>
-  </si>
-  <si>
-    <t>0.17</t>
-  </si>
-  <si>
-    <t>Surfing Community</t>
-  </si>
-  <si>
-    <t>Environmental</t>
-  </si>
-  <si>
-    <t>Surfing quality</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>Tourist Sector</t>
   </si>
   <si>
     <t>Railway functionality</t>
@@ -1017,24 +974,24 @@
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Berekening" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Controlecel" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Gekoppelde cel" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Goed" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Invoer" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Kop 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Kop 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Kop 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Kop 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Neutraal" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Notitie" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Ongeldig" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Titel" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Totaal" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Uitvoer" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Verklarende tekst" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Waarschuwingstekst" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1050,7 +1007,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1366,610 +1323,687 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E21EC2-64DE-445B-8154-60469756B239}">
-  <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1640625" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.1640625" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" customWidth="1"/>
     <col min="15" max="15" width="10.6640625" customWidth="1"/>
     <col min="16" max="16" width="15" customWidth="1"/>
     <col min="17" max="17" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="2">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="2">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="2">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D5" s="2">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>7</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="2">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2">
+        <v>8</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="2">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D12" s="2">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2">
+        <v>7</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="2">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="2">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="2">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2">
+        <v>7</v>
+      </c>
+      <c r="F15" s="2">
+        <v>7</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <f>SUM(G12:G15)</f>
+        <v>1.0000000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="2">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E19" s="2">
+        <v>4</v>
+      </c>
+      <c r="F19" s="2">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2">
+        <v>7</v>
+      </c>
+      <c r="F20" s="2">
+        <v>7</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="2">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="2">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2">
         <v>9</v>
       </c>
-      <c r="C3">
+      <c r="F22" s="2">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="2">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2">
+        <v>7</v>
+      </c>
+      <c r="F23" s="2">
+        <v>7</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="2">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2">
+        <v>5</v>
+      </c>
+      <c r="E24" s="2">
+        <v>7</v>
+      </c>
+      <c r="F24" s="2">
+        <v>6</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="2">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2">
+        <v>7</v>
+      </c>
+      <c r="E25" s="2">
+        <v>7</v>
+      </c>
+      <c r="F25" s="2">
+        <v>7</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2</v>
+      </c>
+      <c r="C26" s="2">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2">
+        <v>4</v>
+      </c>
+      <c r="F26" s="2">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="2">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2">
+        <v>6</v>
+      </c>
+      <c r="F27" s="2">
+        <v>8</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="2">
+        <v>3</v>
+      </c>
+      <c r="C28" s="2">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2">
+        <v>6</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4</v>
+      </c>
+      <c r="F28" s="2">
+        <v>6</v>
+      </c>
+      <c r="G28" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>100</v>
+      </c>
+      <c r="C31">
+        <v>100</v>
+      </c>
+      <c r="D31">
         <v>80</v>
       </c>
-      <c r="D3">
+      <c r="E31">
         <v>100</v>
       </c>
-      <c r="E3">
+      <c r="F31">
+        <v>40</v>
+      </c>
+      <c r="G31">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32">
+        <v>90</v>
+      </c>
+      <c r="C32">
+        <v>60</v>
+      </c>
+      <c r="D32">
+        <v>80</v>
+      </c>
+      <c r="E32">
+        <v>90</v>
+      </c>
+      <c r="F32">
+        <v>70</v>
+      </c>
+      <c r="G32">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33">
+        <v>50</v>
+      </c>
+      <c r="C33">
+        <v>40</v>
+      </c>
+      <c r="D33">
+        <v>100</v>
+      </c>
+      <c r="E33">
+        <v>50</v>
+      </c>
+      <c r="F33">
+        <v>30</v>
+      </c>
+      <c r="G33">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34">
+        <v>80</v>
+      </c>
+      <c r="C34">
+        <v>80</v>
+      </c>
+      <c r="D34">
         <v>10</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="E34">
+        <v>80</v>
+      </c>
+      <c r="F34">
+        <v>30</v>
+      </c>
+      <c r="G34">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>60</v>
+      </c>
+      <c r="C35">
+        <v>50</v>
+      </c>
+      <c r="D35">
+        <v>90</v>
+      </c>
+      <c r="E35">
+        <v>50</v>
+      </c>
+      <c r="F35">
+        <v>60</v>
+      </c>
+      <c r="G35">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>11</v>
       </c>
-      <c r="C4">
-        <v>25</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
+      <c r="B36">
+        <v>70</v>
+      </c>
+      <c r="C36">
         <v>80</v>
       </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
+      <c r="D36">
+        <v>95</v>
+      </c>
+      <c r="E36">
         <v>50</v>
       </c>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>80</v>
-      </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>75</v>
-      </c>
-      <c r="F7">
-        <v>75</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>80</v>
-      </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>70</v>
-      </c>
-      <c r="D10">
-        <v>100</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11">
-        <v>100</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>75</v>
-      </c>
-      <c r="F11">
-        <v>75</v>
-      </c>
-      <c r="G11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12">
-        <v>80</v>
-      </c>
-      <c r="D12">
-        <v>100</v>
-      </c>
-      <c r="E12">
-        <v>20</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13">
-        <v>100</v>
-      </c>
-      <c r="D13">
-        <v>50</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>100</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15">
-        <v>100</v>
-      </c>
-      <c r="D15">
-        <v>90</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>100</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-      <c r="G16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>80</v>
-      </c>
-      <c r="F17">
-        <v>100</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18">
-        <v>70</v>
-      </c>
-      <c r="D18">
-        <v>100</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" s="2">
-        <v>2</v>
-      </c>
-      <c r="C27" s="2">
-        <v>10</v>
-      </c>
-      <c r="D27" s="2">
-        <v>5</v>
-      </c>
-      <c r="E27" s="2">
-        <v>5</v>
-      </c>
-      <c r="F27" s="2">
-        <v>5</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" s="2">
-        <v>9</v>
-      </c>
-      <c r="C28" s="2">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2">
-        <v>8</v>
-      </c>
-      <c r="F28" s="2">
-        <v>8</v>
-      </c>
-      <c r="G28" s="2">
+      <c r="F36">
+        <v>60</v>
+      </c>
+      <c r="G36">
         <v>0.1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" s="2">
-        <v>6</v>
-      </c>
-      <c r="C29" s="2">
-        <v>10</v>
-      </c>
-      <c r="D29" s="2">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2">
-        <v>5</v>
-      </c>
-      <c r="F29" s="2">
-        <v>8</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B30" s="2">
-        <v>10</v>
-      </c>
-      <c r="C30" s="2">
-        <v>3</v>
-      </c>
-      <c r="D30" s="2">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2">
-        <v>8</v>
-      </c>
-      <c r="F30" s="2">
-        <v>8</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="2">
-        <v>2</v>
-      </c>
-      <c r="C31" s="2">
-        <v>10</v>
-      </c>
-      <c r="D31" s="2">
-        <v>5</v>
-      </c>
-      <c r="E31" s="2">
-        <v>5</v>
-      </c>
-      <c r="F31" s="2">
-        <v>7</v>
-      </c>
-      <c r="G31" s="2">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B32" s="2">
-        <v>2</v>
-      </c>
-      <c r="C32" s="2">
-        <v>10</v>
-      </c>
-      <c r="D32" s="2">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2">
-        <v>8</v>
-      </c>
-      <c r="F32" s="2">
-        <v>8</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="2">
-        <v>9</v>
-      </c>
-      <c r="C33" s="2">
-        <v>10</v>
-      </c>
-      <c r="D33" s="2">
-        <v>5</v>
-      </c>
-      <c r="E33" s="2">
-        <v>5</v>
-      </c>
-      <c r="F33" s="2">
-        <v>5</v>
-      </c>
-      <c r="G33" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G34">
-        <f>SUM(G27:G33)</f>
-        <v>0.99999999999999989</v>
       </c>
     </row>
   </sheetData>
@@ -1981,48 +2015,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A898AA9E-6EE8-44A9-9DEF-7D9FA314DBCA}">
   <dimension ref="B2:H15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="48" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2">
         <v>8</v>
@@ -2043,9 +2077,9 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2">
         <v>8</v>
@@ -2066,9 +2100,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="C7" s="2">
         <v>8</v>
@@ -2089,9 +2123,9 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2">
         <v>5</v>
@@ -2112,50 +2146,50 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H9">
         <f>SUM(H5:H8)</f>
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2166,43 +2200,43 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E73D97-BC3F-49A1-B8F4-F095906B505B}">
   <dimension ref="A2:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" customWidth="1"/>
     <col min="6" max="6" width="19.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2">
         <v>3</v>
@@ -2223,9 +2257,9 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
         <v>8</v>
@@ -2246,9 +2280,9 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2">
         <v>8</v>
@@ -2269,9 +2303,9 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2">
         <v>8</v>
@@ -2292,9 +2326,9 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2">
         <v>5</v>
@@ -2315,9 +2349,9 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
@@ -2338,9 +2372,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
@@ -2361,9 +2395,9 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -2384,9 +2418,9 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2">
         <v>8</v>
@@ -2407,9 +2441,9 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
@@ -2430,7 +2464,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G13">
         <f>SUM(G3:G12)</f>
         <v>1</v>
@@ -2444,54 +2478,54 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A57D4CE-8BDF-4BD2-8CFC-2B5D7CFE333B}">
   <dimension ref="B2:I24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
         <v>41</v>
       </c>
-      <c r="I3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -2512,12 +2546,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>90</v>
@@ -2538,12 +2572,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -2564,12 +2598,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>80</v>
@@ -2590,12 +2624,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D8">
         <v>60</v>
@@ -2616,12 +2650,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>70</v>
@@ -2642,193 +2676,193 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G18" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="I19">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="I20">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="I21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="G22" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="H22" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="I22">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="G23" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" t="s">
         <v>38</v>
       </c>
-      <c r="C24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" t="s">
-        <v>69</v>
-      </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="H24" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="I24">
         <v>10</v>
